--- a/artfynd/A 11894-2022 artfynd.xlsx
+++ b/artfynd/A 11894-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11894-2022 artfynd.xlsx
+++ b/artfynd/A 11894-2022 artfynd.xlsx
@@ -4314,7 +4314,7 @@
         <v>96998046</v>
       </c>
       <c r="B33" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550800.7421419449</v>
+        <v>550801</v>
       </c>
       <c r="R33" t="n">
-        <v>6946356.722074904</v>
+        <v>6946357</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4392,19 +4392,9 @@
           <t>2021-08-22</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-08-22</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 11894-2022 artfynd.xlsx
+++ b/artfynd/A 11894-2022 artfynd.xlsx
@@ -4314,7 +4314,7 @@
         <v>96998046</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 11894-2022 artfynd.xlsx
+++ b/artfynd/A 11894-2022 artfynd.xlsx
@@ -4314,7 +4314,7 @@
         <v>96998046</v>
       </c>
       <c r="B33" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 11894-2022 artfynd.xlsx
+++ b/artfynd/A 11894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996989</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996990</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996996</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996997</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996998</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996999</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997151</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997586</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996951</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996952</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996957</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996959</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997412</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997488</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997489</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997490</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997491</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997512</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997513</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997514</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997515</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997516</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997517</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996920</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996921</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996922</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996923</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,6 +3754,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96998056</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3718,6 +3868,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96998057</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3827,6 +3982,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96998058</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96998059</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4045,6 +4210,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96998060</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4154,6 +4324,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96998063</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4263,6 +4438,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96998046</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4364,6 +4544,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997597</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4465,8 +4650,52 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997172</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>